--- a/www/download/COUNTRY.POL.rpO1.xlsx
+++ b/www/download/COUNTRY.POL.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>Polônia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>2.42412495735975</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>2.69164505131081</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>3.26679958645285</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>3.47270458662722</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>3.95882797122747</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>4.33914775167024</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>4.09198792933865</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>4.07830354787578</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>3.88742031091487</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>3.6387453558442</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>3.23185325766701</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>3.10019827648708</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>2.75793607453417</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.37751058134273</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.09692432732096</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14.735</t>
+          <t>2.03030157377649</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.021</t>
+          <t>1.93028328564004</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15.439</t>
+          <t>1.8449030975248</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>1.81662949709829</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15.375</t>
+          <t>1.9126472237251</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>15.018</t>
+          <t>1.85696627450787</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14.195</t>
+          <t>1.80696401820505</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.766</t>
+          <t>1.82107078950656</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>13.606</t>
+          <t>2.12574054646523</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>13.773</t>
+          <t>1.93582172917666</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>14.075</t>
+          <t>2.020591406409</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>1.98799230773746</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>15.174</t>
+          <t>1.90100391975953</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>15.784</t>
+          <t>1.8913578517268</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>15.786</t>
+          <t>1.88174267697936</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8.714</t>
+          <t>3.85798483185412</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.725</t>
+          <t>3.71377254984281</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.863</t>
+          <t>3.60165494148052</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>8.938</t>
+          <t>3.58115408667379</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8.896</t>
+          <t>3.73571062997009</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.354</t>
+          <t>3.65075626199591</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10.207</t>
+          <t>3.56750231026184</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>3.71859742037474</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>9.891</t>
+          <t>3.92794677045729</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10.084</t>
+          <t>3.82386726675845</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10.436</t>
+          <t>3.88114759430835</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>10.963</t>
+          <t>3.79290649191128</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>11.605</t>
+          <t>3.71399850308858</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>12.126</t>
+          <t>3.54705789543529</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>12.207</t>
+          <t>3.48985613713279</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>28305.086</t>
+          <t>5.28481800716906</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28879.294</t>
+          <t>5.10659979616198</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29662.441</t>
+          <t>4.97085159114657</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30129.465</t>
+          <t>4.94795294956956</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29829.818</t>
+          <t>5.15434257078814</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>28892.502</t>
+          <t>5.05464021290778</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26456.571</t>
+          <t>5.01447564258073</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>25507.399</t>
+          <t>5.24087168504369</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>25162.379</t>
+          <t>3.45713800137895</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25538.377</t>
+          <t>5.38436988170693</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>25769.666</t>
+          <t>5.32760339865991</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>26509.432</t>
+          <t>5.22101964018991</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>27585.81</t>
+          <t>5.22023782820005</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>28604.274</t>
+          <t>4.67261629186158</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>28297.15</t>
+          <t>4.58511246440074</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15014.242</t>
+          <t>13843774276424.4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15032.708</t>
+          <t>13499873800184.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15287.945</t>
+          <t>13827156845664.3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15407.358</t>
+          <t>17438089765289.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15801.55</t>
+          <t>18464987413550.7</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>16365.614</t>
+          <t>16401693412935</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17542.312</t>
+          <t>17144240586663.2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16854.515</t>
+          <t>15546180553684.2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>16906.382</t>
+          <t>15733593692813.6</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>17319.251</t>
+          <t>14822289811671.3</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>17709.691</t>
+          <t>15576321315040.1</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>18612.378</t>
+          <t>14374065485543</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>19705.785</t>
+          <t>13365066979711.1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20418.937</t>
+          <t>11855355520668.5</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>20070.824</t>
+          <t>8893588815403.04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>992612445013.488</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>1034165849321.21</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>1087656456052.21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>1332215520000.25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>1362891225996.76</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>1526057046708.87</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>1846284545190.45</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>1764602609531.7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23.21</t>
+          <t>1787547845313.2</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>1639006398305.5</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>1728116823945.85</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>1648563616071.46</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>1540883896642.18</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>1514779094297.77</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>1171854964634.59</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>1347041346.36765</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>1236987201.8533</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>1320885421.08745</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>1559383402.97991</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>1734744780.81617</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>1608780662.00374</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>71.37</t>
+          <t>1569171163.33339</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>1419286420.0282</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>68.27</t>
+          <t>1302106755.27855</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>67.04</t>
+          <t>995482423.054483</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>66.25</t>
+          <t>887437344.208594</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>728505196.527313</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>534636707.742745</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>382856071.543584</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>371343522.94721</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>328586.634851649</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>361205.151239148</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>369929.407680953</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>428484.969084629</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>431357.1905084</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>326198.993764101</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>324708.742603435</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>310146.821070063</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>319590.12326562</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>353276.001067812</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>418793.50846293</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>440866.291850127</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>532760.961989186</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>691250.951591501</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>557006.145015977</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>622370.164969478</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>681686.049756424</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>683544.892531379</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>782319.669949754</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>772178.121150828</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>604775.073111376</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>597757.966730636</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>566716.615706512</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>602638.192425798</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>17.76</t>
+          <t>682367.131294563</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>802686.23663643</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>19.61</t>
+          <t>859230.120373511</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>1065420.17097542</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>1259131.73186053</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>983402.793916917</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.64</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>76.03</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>74.06</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>73.47</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>32576.0339670849</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>36808.2738750884</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>39096.1452575262</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>42666.8431366874</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>43137.6454940369</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>44093.3977422624</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>46807.1881066426</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>49867.4481896885</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>55784.322017333</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>63773.1867390281</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>72651.060032066</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>78521.8156547962</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>95388.6672297573</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.42412495735975</t>
+          <t>113914.002664022</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.69164505131081</t>
+          <t>118533.112808602</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.26679958645285</t>
+          <t>122716.000547456</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3.47270458662722</t>
+          <t>149044.070527192</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3.95882797122747</t>
+          <t>153202.700764025</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.33914775167024</t>
+          <t>163143.118708253</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.09198792933865</t>
+          <t>180891.241470269</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4.07830354787578</t>
+          <t>178612.542085298</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.88742031091487</t>
+          <t>180728.337982085</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3.6387453558442</t>
+          <t>162538.56664209</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3.23185325766701</t>
+          <t>165587.116501619</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3.10019827648708</t>
+          <t>150376.598899148</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.75793607453417</t>
+          <t>132778.731108599</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.37751058134273</t>
+          <t>124921.992305478</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3.09692432732096</t>
+          <t>96000.9637850189</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>-644585304112.516</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>-569052671234.97</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>-605963732853.954</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>-786975127317.025</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-889940444041.413</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>-493290702413.479</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>-456305623489.226</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>-321683904457.045</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>-256273988967.315</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>-57699678548.0375</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>-126154647602.614</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>-14186618343.5057</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>44397191353.4699</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>76753119968.9588</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>138417226233.053</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>-622422413668.264</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>-578090972027.828</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>-660226973217.824</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>-886360063017.578</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>-892355270575.966</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-484736163210.539</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>-392689888820.297</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>-243651931874.671</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>-177301879694.281</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>9201788312.10323</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>-58373865567.9713</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>52043693899.0788</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>62361757208.0046</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>105784417918.899</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>146177836574.022</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>-22162890444.2515</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>9038300792.85837</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>54263240363.8697</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>99384935700.5526</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>2414826534.55301</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>-8554539202.9399</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-63615734668.9291</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>-78031972582.375</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>-78972109273.0347</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>-66901466860.1407</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>-67780782034.6428</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>-66230312242.5845</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>-17964565854.5348</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-29031297949.9405</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-7760610340.96984</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>510616.969712744</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>515557.743228985</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>519981.858472158</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>628141.498793268</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>665992.030453</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>695308.815177478</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>750199.252405269</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>751267.919899943</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>781478.352623465</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>682454.047155728</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>699965.396087752</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>622944.181201927</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>537820.144707886</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>493411.261979179</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>371200.348898303</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>676903.752942489</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>670138.052707524</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>697231.667360572</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>875826.701164321</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>958396.278042174</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>877584.18511418</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>1012342.60144086</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>977524.592835105</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>987730.892654381</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>900967.303166356</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>928107.162725087</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>836639.070629479</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>735328.991916472</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>688143.572633687</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>538560.958431888</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>203.03</t>
+          <t>32273.0904982147</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>193.03</t>
+          <t>34981.3289632228</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>184.49</t>
+          <t>36927.2736772823</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>181.66</t>
+          <t>44720.5519158438</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>191.26</t>
+          <t>40164.013906437</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>185.7</t>
+          <t>46634.020946017</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>180.7</t>
+          <t>51317.5554726516</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>182.11</t>
+          <t>55901.6892476891</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>212.57</t>
+          <t>71127.0532923045</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>193.58</t>
+          <t>93780.533903888</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>202.06</t>
+          <t>112144.879107038</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>198.8</t>
+          <t>137120.586339317</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>190.1</t>
+          <t>174806.150409671</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>189.14</t>
+          <t>213238.291851392</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>188.17</t>
+          <t>165890.059090342</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>385.8</t>
+          <t>1716743807824.65</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>371.38</t>
+          <t>1624874766209.99</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>360.17</t>
+          <t>1773126603457.18</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>358.12</t>
+          <t>2356531681840.81</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>373.57</t>
+          <t>2337710045570.6</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>365.08</t>
+          <t>2431911440542.76</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>356.75</t>
+          <t>2689907453433.67</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>371.86</t>
+          <t>2684879856662.38</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>392.79</t>
+          <t>3163207124980.55</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>382.39</t>
+          <t>3232349401785.6</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>388.11</t>
+          <t>3476154228427.91</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>379.29</t>
+          <t>3457068285660.83</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>371.4</t>
+          <t>3204799805533.32</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>354.71</t>
+          <t>2786123699399.48</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>348.99</t>
+          <t>2101208909778.85</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>528.48</t>
+          <t>27947.9236956013</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>510.66</t>
+          <t>35401.5459044805</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>497.09</t>
+          <t>40806.6375670446</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>494.8</t>
+          <t>50367.1160082573</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>515.43</t>
+          <t>47847.6881637181</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>505.46</t>
+          <t>55163.6032673991</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>501.45</t>
+          <t>55959.0223500399</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>524.09</t>
+          <t>60262.9530736781</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>345.71</t>
+          <t>73868.5240165445</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>538.44</t>
+          <t>95764.783608164</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>532.76</t>
+          <t>109753.160494378</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>522.1</t>
+          <t>137410.611722296</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>522.02</t>
+          <t>179302.879672821</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>467.26</t>
+          <t>225277.374472069</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>458.51</t>
+          <t>158895.392346397</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9974312.18</t>
+          <t>914303133070.786</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10065875.634</t>
+          <t>1069497968971.71</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10764350.543</t>
+          <t>1296483943499.89</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>13838412.209</t>
+          <t>1781310078619.11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>14735342.775</t>
+          <t>1758014824896.75</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>13179120.5</t>
+          <t>2326746086425.54</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14370000.759</t>
+          <t>2460720494015.15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>13456896.802</t>
+          <t>2568939587085.28</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>13439165.299</t>
+          <t>3028754694570.86</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>12409292.957</t>
+          <t>3246974647091.62</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>13062644.262</t>
+          <t>3272498783222.28</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>12156282.032</t>
+          <t>3450893911734.22</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>11158029.189</t>
+          <t>3340663150222.08</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>10861414.472</t>
+          <t>3043879359217.82</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>8501806.967</t>
+          <t>2136148307001.48</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4449363.089</t>
+          <t>4325.16680261337</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4498086.642</t>
+          <t>-420.216941257668</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4608703.208</t>
+          <t>-3879.3638897623</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>5614579.973</t>
+          <t>-5646.5640924135</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5924665.103</t>
+          <t>-7683.67425728115</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6503988.188</t>
+          <t>-8529.58232138208</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7656983.69</t>
+          <t>-4641.4668773883</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7422151.415</t>
+          <t>-4361.26382598899</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7729446.09</t>
+          <t>-2741.47072423993</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6881730.121</t>
+          <t>-1984.24970427598</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>7305048.863</t>
+          <t>2391.71861266029</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6829274.764</t>
+          <t>-290.02538297949</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>6241348.997</t>
+          <t>-4496.72926315063</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5983006.281</t>
+          <t>-12039.0826206775</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>4531131.299</t>
+          <t>6994.66674394492</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13843774.276</t>
+          <t>802440674753.859</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13499873.8</t>
+          <t>555376797238.28</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13827156.846</t>
+          <t>476642659957.299</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>17438089.765</t>
+          <t>575221603221.699</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>18464987.414</t>
+          <t>579695220673.849</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>16401693.413</t>
+          <t>105165354117.222</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17144240.587</t>
+          <t>229186959418.518</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>15546180.554</t>
+          <t>115940269577.097</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>15733593.693</t>
+          <t>134452430409.69</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>14822289.812</t>
+          <t>-14625245306.0168</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>15576321.315</t>
+          <t>203655445205.636</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>14374065.486</t>
+          <t>6174373926.61188</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>13365066.98</t>
+          <t>-135863344688.759</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>11855355.521</t>
+          <t>-257755659818.34</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8893588.815</t>
+          <t>-34939397222.6299</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>66902.07927</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>72393.64547</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>71058.53687</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>76788.56472</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>72655.5947</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>73159.29721</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.598</t>
+          <t>78760.74134</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>80203.44746</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>89780.8755</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>107873.44568</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.803</t>
+          <t>127833.46508</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>143520.73575</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>179221.20543</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.259</t>
+          <t>222432.85622</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>184289.98954</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>7308960.903</t>
+          <t>-0.0758416078262403</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7153181.379</t>
+          <t>-0.0757022375858964</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7483154.359</t>
+          <t>-0.0850823533383653</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>9551030.916</t>
+          <t>-0.0950725202021011</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10314984.167</t>
+          <t>-0.103577164804921</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8846621.042</t>
+          <t>-0.0227658275929951</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9312941.213</t>
+          <t>0.00327696236818935</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8507953.261</t>
+          <t>0.0137438063582751</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8343814.267</t>
+          <t>0.020810741731105</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>7673815.211</t>
+          <t>0.039911932707189</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>8126789.715</t>
+          <t>0.0466037532633269</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7375254.66</t>
+          <t>0.0590318048770405</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>6683171.706</t>
+          <t>0.0661443494075685</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>6508473.719</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>5037390.225</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>55322.2305835788</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>64243.2401122611</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>65817.015680837</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>72614.0086731007</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>69775.9544477548</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>69008.2517646412</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>78158.5883185697</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>77618.7934548832</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>82843.1121536122</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>91917.3966184302</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>108968.128312447</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>121452.55447037</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>151637.307249389</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>199382.989951675</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>158759.834349227</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>992612.445</t>
+          <t>122419.634625984</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1034165.849</t>
+          <t>136365.178028398</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1087656.456</t>
+          <t>138702.568470208</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1332215.52</t>
+          <t>158088.637722025</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1362891.226</t>
+          <t>154789.819536808</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1526057.047</t>
+          <t>119603.910053449</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1846284.545</t>
+          <t>121330.985757966</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1764602.61</t>
+          <t>117856.895027572</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1787547.845</t>
+          <t>123175.866337015</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1639006.398</t>
+          <t>135218.424879093</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1728116.824</t>
+          <t>158798.181727026</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1648563.616</t>
+          <t>171313.241181191</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1540883.897</t>
+          <t>208900.965393392</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1514779.094</t>
+          <t>271054.618660394</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1171854.965</t>
+          <t>216652.208613619</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>426619.898502123</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>464177.552923918</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>452635.807269903</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>494548.346133708</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>480450.148587969</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>486745.455241911</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>539597.482887317</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>553798.994567247</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>601526.101635378</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>671938.500413658</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>785564.806423376</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>855912.421604851</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>1042806.03475039</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1347.041</t>
+          <t>122419.634625984</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1236.987</t>
+          <t>129436.259353255</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1320.885</t>
+          <t>142833.683496869</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1559.383</t>
+          <t>160530.459879988</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1734.745</t>
+          <t>177550.859327161</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1608.781</t>
+          <t>134371.612221007</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1569.171</t>
+          <t>123613.532384102</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1419.286</t>
+          <t>120635.015915468</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1302.107</t>
+          <t>119602.990802215</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>995.482</t>
+          <t>112883.529539395</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>887.437</t>
+          <t>117762.490628025</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>728.505</t>
+          <t>119156.286087209</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>534.637</t>
+          <t>122537.678036396</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>382.856</t>
+          <t>135611.742378845</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>371.344</t>
+          <t>134732.675475313</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>55322.2305835788</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>60999.3820175542</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>66319.2242131613</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>70225.6586635871</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>72995.5337176053</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>73378.843003773</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>75466.455410065</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>72914.3072583563</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>73912.6866171794</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>72988.5945707342</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>75529.0483650772</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>80455.9358743324</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>87439.8862806087</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>97107.2575900012</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>93588.395627913</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>220.494934016407</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1668.99448160193</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>584.825569792097</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-4351.11449202529</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-6626.01872680818</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>33012.2346265512</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>48575.428752034</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>57478.7543324281</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>68302.5263629852</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>90591.5509509075</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>109261.328442974</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>129047.870718809</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>164364.393956608</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>198544.131219606</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>168885.787786381</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4449363088985.94</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4498086642349.93</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4608703208010.43</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>5614579972813.75</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>5924665102909.88</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6503988188051.65</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7656983689599.62</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>7422151414651.49</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7729446090128.17</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6881730120708.93</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>7305048863190.61</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>6829274764098.6</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>6241348997320.55</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5983006280507.12</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>4531131298896.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>9974312180358.17</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10065875634498.6</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10764350542879.7</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>13838412209076.7</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>14735342774898.4</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>13179120499952.2</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>14370000758932.8</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>13456896802345.9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>13439165298544.8</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>12409292956701.2</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>13062644261774.2</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>12156282032339.3</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>11158029189138.9</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>10861414471635.7</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>8501806966688.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7308960903290.08</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>7153181379386.12</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>7483154358575.5</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>9551030916115.32</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>10314984166621.3</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>8846621041772.6</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9312941213035.73</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>8507953260723.47</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>8343814266827.46</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>7673815210590.79</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>8126789715252.38</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>7375254660145.64</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>6683171705527.1</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>6508473718638.19</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5037390225111.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>14735200</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>15020600</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>15438700</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>15800400</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>15375000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>15017500</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14194800</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>13766300</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>13606100</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>13773300</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>14074500</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>14529900</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>15174200</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>15783645.889573</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>15786155.3712382</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>8713700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8724700</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>8863200</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>8938400</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>8896000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>9354100</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10206600</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>9879500</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>9890800</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>10083800</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>10436300</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>10962900</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>11604900</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>12125800</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>12206700</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>28305086293.1525</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>28879294419.0028</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>29662440618.8973</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>30129464561.2833</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>29829817522.3089</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>28892502127.8591</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>26456570789.3266</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>25507398965.6909</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>25162379461.1629</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>25538377300.9695</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>25769666149.1946</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>26509432484.7037</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>27585810137.3996</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>28604273526.7837</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>28297149673.6112</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>15014241815.3346</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>15032707867.3007</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>15287944968.716</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>15407358482.0686</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>15801550161.6009</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>16365614284.9565</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>17542311839.8331</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>16854514610.4582</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>16906382225.1846</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>17319250893.9937</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>17709690793.7366</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>18612378276.4895</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>19705785159.2337</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>20418936958.2142</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>20070824201.2121</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.214380705497248</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.230918530591076</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.232116469535008</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.277251635777324</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.288095700635141</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.295513218664395</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.304555318021329</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.299157843309884</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.319155072994049</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.713749162074466</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.704022519621681</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.682689167535268</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.67044334674335</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.662467146601343</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.656010408643502</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.646989663617845</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.649286049704992</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.631515982679652</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0718701324282859</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0650589497872431</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0851943629297249</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0523050174793255</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0494371527635151</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0484763726921036</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0484550183608254</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0515561069851239</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0493289443262993</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.122043564712389</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.122043564712389</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.122043564712389</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.122043564712389</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.122043564712389</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.122043564712389</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.133271213275365</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.141719800156731</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.156956740225659</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.17755604537419</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.188549726720077</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.196122066802558</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.201049411020539</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.203680734714193</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.220249348393439</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.776542665775152</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.776542665775152</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.776542665775152</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.776542665775152</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.776542665775152</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.776542665775152</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.766039863441556</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.766362663654355</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.760297201690192</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.746768404993518</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.740576730084175</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.734687391152289</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.728261829122457</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.723964954159925</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.70997595536251</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.101413769512459</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.101413769512459</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.101413769512459</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.101413769512459</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.101413769512459</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.101413769512459</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.100688923283079</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0919175361889144</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0827460580841493</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0756755496322918</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.070873543195748</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0691905420451524</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0706887598570042</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0723543111258817</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0697746962440506</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>264793.69278</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>299043.88961</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>300257.78319</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>329628.38256</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>320451.15519</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>335095.52743</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>374515.27799</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>384060.67339</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>424185.41114</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>509518.75332</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>603836.20512</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>695167.79525</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>883621.63806</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1111403.68187</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>865782.85723</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>122640.12956</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>138034.17251</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>139287.39404</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>153737.52323</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>148163.80081</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>152616.14468</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>169906.41451</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>175335.64936</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>191478.3927</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>225809.97583</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>268059.51017</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>300361.1119</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>373265.35935</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>469598.74988</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>385537.9964</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1034179.94551128</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1062964.04076036</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1105245.96981106</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1156671.62373569</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1210867.2853591</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1263983.15299466</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1302898.57441767</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1332205.72669073</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1359887.13054996</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1391996.40648563</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1428955.21337048</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1479953.99581784</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1549336.65184272</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
